--- a/artfynd/A 67278-2021 artfynd.xlsx
+++ b/artfynd/A 67278-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67278-2021 artfynd.xlsx
+++ b/artfynd/A 67278-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,237 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123704273</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100645</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hacksta, Åkersberga, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>687311</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6599782</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anna-Mi Wendel</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna-Mi Wendel</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123704184</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56432</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hacksta, Åkersberga, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>687311</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6599782</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Mi Wendel</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Mi Wendel</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 67278-2021 artfynd.xlsx
+++ b/artfynd/A 67278-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123704273</v>
+        <v>123704184</v>
       </c>
       <c r="B3" t="n">
-        <v>100645</v>
+        <v>56438</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,31 +815,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -910,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123704184</v>
+        <v>123704273</v>
       </c>
       <c r="B4" t="n">
-        <v>56432</v>
+        <v>100662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,40 +935,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 67278-2021 artfynd.xlsx
+++ b/artfynd/A 67278-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>123704184</v>
       </c>
       <c r="B3" t="n">
-        <v>56438</v>
+        <v>56441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>123704273</v>
       </c>
       <c r="B4" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 67278-2021 artfynd.xlsx
+++ b/artfynd/A 67278-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123704184</v>
+        <v>123704273</v>
       </c>
       <c r="B3" t="n">
-        <v>56441</v>
+        <v>100682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,40 +815,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -919,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123704273</v>
+        <v>123704184</v>
       </c>
       <c r="B4" t="n">
-        <v>100680</v>
+        <v>56441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +926,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 67278-2021 artfynd.xlsx
+++ b/artfynd/A 67278-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123704273</v>
+        <v>123704184</v>
       </c>
       <c r="B3" t="n">
-        <v>100682</v>
+        <v>56441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,31 +815,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -910,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123704184</v>
+        <v>123704273</v>
       </c>
       <c r="B4" t="n">
-        <v>56441</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,40 +935,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 67278-2021 artfynd.xlsx
+++ b/artfynd/A 67278-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123704184</v>
+        <v>123704273</v>
       </c>
       <c r="B3" t="n">
-        <v>56441</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,40 +815,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -919,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123704273</v>
+        <v>123704184</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
+        <v>56441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +926,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 67278-2021 artfynd.xlsx
+++ b/artfynd/A 67278-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123704273</v>
+        <v>123704184</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>56441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,31 +815,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -910,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123704184</v>
+        <v>123704273</v>
       </c>
       <c r="B4" t="n">
-        <v>56441</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,40 +935,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
